--- a/AAII_Financials/Yearly/TLK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TLK_YR_FIN.xlsx
@@ -4093,10 +4093,10 @@
         <v>2070000</v>
       </c>
       <c r="E83" s="3">
-        <v>1953200</v>
+        <v>1957900</v>
       </c>
       <c r="F83" s="3">
-        <v>1957800</v>
+        <v>1958600</v>
       </c>
       <c r="G83" s="3">
         <v>1993000</v>
